--- a/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
+++ b/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>51개(ATT&amp;CK 전술 12단계) — 위험도 매우 높음 17 · 높음 12 · 보통 21 · 낮음 1</t>
+          <t>51개(ATT&amp;CK 전술 12단계) — 위험도 매우 높음 6 · 높음 15 · 보통 25 · 낮음 5</t>
         </is>
       </c>
     </row>
@@ -815,17 +815,17 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[EF] 반출</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ENT-CA-01.1</t>
+          <t>ENT-EF-02</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>OS 자격증명 덤프(LSASS 메모리)</t>
+          <t>정상 웹 서비스·대체 프로토콜 경유 반출</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -835,38 +835,42 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>CL-EF-02</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ENT-CA-03</t>
+          <t>ENT-IA-05</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Kerberoasting·AS-REP 로스팅</t>
+          <t>신뢰 관계(MSP·협력사·연동) 악용</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -876,12 +880,12 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>신뢰·공급 관계 경유 · 정상 인증 위장</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>ID-TS-02</t>
+          <t>SC-CS-03</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -901,17 +905,17 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-IM-01</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
+          <t>데이터 암호화(사람 운영 랜섬웨어)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -921,12 +925,12 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -934,25 +938,29 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>CL-IM-01, OT-IM-02</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-IM-02</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드(커널)</t>
+          <t>복구 방해(섀도 카피·백업 삭제)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -962,17 +970,17 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -983,17 +991,17 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>[EF] 반출</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ENT-EF-01</t>
+          <t>ENT-IM-05</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>C2 채널 경유 반출</t>
+          <t>금전 탈취·이중 협박 갈취</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1003,12 +1011,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1016,25 +1024,29 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>CL-IM-05, ID-IM-01</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>[EF] 반출</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ENT-EF-02</t>
+          <t>ENT-LM-04</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>정상 웹 서비스·대체 프로토콜 경유 반출</t>
+          <t>원격 서비스 취약점 악용(웜 확산)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1044,22 +1056,22 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
+          <t>시그니처 회피</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>CL-EF-02</t>
+          <t>OT-LM-06</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
@@ -1069,32 +1081,32 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1</t>
+          <t>ENT-C2-01.2</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>PowerShell 악용(파일리스 실행)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>응용 계층 프로토콜(HTTPS) C2</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -1110,37 +1122,37 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-03</t>
+          <t>ENT-C2-05</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>인그레스 도구 전송(페이로드 반입)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
@@ -1151,77 +1163,73 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[CA] 자격증명 접근</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
+          <t>ENT-CA-01.1</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>OS 자격증명 덤프(LSASS 메모리)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>경계 밖·비관리 장비 · 신뢰·공급 관계 경유</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>CL-IA-01</t>
-        </is>
-      </c>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-02</t>
+          <t>ENT-DE-01.1</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 경계 밖·비관리 장비</t>
+          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1229,44 +1237,40 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>CL-IA-02, ID-AU-04</t>
-        </is>
-      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-05</t>
+          <t>ENT-DE-01.2</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>신뢰 관계(MSP·협력사·연동) 악용</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>취약·악성 드라이버 로드(커널)</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>신뢰·공급 관계 경유 · 정상 인증 위장</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1274,44 +1278,40 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>SC-CS-03</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-01</t>
+          <t>ENT-DE-03</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>데이터 암호화(사람 운영 랜섬웨어)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>시그니처 회피</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1319,39 +1319,35 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>CL-IM-01, OT-IM-02</t>
-        </is>
-      </c>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-02</t>
+          <t>ENT-DI-01</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>복구 방해(섀도 카피·백업 삭제)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>호스트·시스템·네트워크 구성 탐색</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1372,32 +1368,32 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-05</t>
+          <t>ENT-DI-02</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>금전 탈취·이중 협박 갈취</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>도메인·AD 열거(계정·신뢰·공유)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1405,44 +1401,40 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>CL-IM-05, ID-IM-01</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[EF] 반출</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-01</t>
+          <t>ENT-EF-01</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>C2 채널 경유 반출</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 암호화·정상 채널 은닉</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1458,32 +1450,32 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-02</t>
+          <t>ENT-EX-01.1</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>PowerShell 악용(파일리스 실행)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1491,54 +1483,50 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>ID-TS-02</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-04</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>원격 서비스 취약점 악용(웜 확산)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피</t>
+          <t>경계 밖·비관리 장비 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>OT-LM-06</t>
+          <t>CL-IA-01</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
@@ -1548,17 +1536,17 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-01.1</t>
+          <t>ENT-IA-02</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>암호화 채널·비표준/정상 포트 위장 C2</t>
+          <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1568,12 +1556,12 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>정상 인증 위장 · 경계 밖·비관리 장비</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1581,25 +1569,29 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>CL-IA-02, ID-AU-04</t>
+        </is>
+      </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-01.2</t>
+          <t>ENT-IM-03</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>응용 계층 프로토콜(HTTPS) C2</t>
+          <t>데이터 파괴·와이퍼</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1609,12 +1601,12 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>서명된 정상 도구 악용 · 커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1622,25 +1614,29 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>OT-IR-01</t>
+        </is>
+      </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-03</t>
+          <t>ENT-LM-01</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
+          <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1650,12 +1646,12 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
+          <t>정상 인증 위장 · 암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -1663,29 +1659,25 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>AI-01-09, CL-C2-01</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-05</t>
+          <t>ENT-LM-02</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>인그레스 도구 전송(페이로드 반입)</t>
+          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1695,53 +1687,57 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr"/>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>ID-TS-02</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-C2-01.1</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>암호화 채널·비표준/정상 포트 위장 C2</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -1757,32 +1753,32 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-C2-03</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>인메모리·반사 코드 로딩</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 시그니처 회피</t>
+          <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -1790,40 +1786,44 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>AI-01-09, CL-C2-01</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-07</t>
+          <t>ENT-C2-04</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>루트킷(사용자·커널 은폐)</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>도메인 프런팅·다단계 프록시</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -1839,32 +1839,32 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-C2-06</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>DNS 경유 C2·터널링</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -1880,32 +1880,32 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[CA] 자격증명 접근</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>ENT-DI-02</t>
+          <t>ENT-CA-03</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>도메인·AD 열거(계정·신뢰·공유)</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>Kerberoasting·AS-REP 로스팅</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -1913,85 +1913,85 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>ID-TS-02</t>
+        </is>
+      </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[CA] 자격증명 접근</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-03</t>
+          <t>ENT-CA-04</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>데이터 파괴·와이퍼</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>입력 캡처·키로깅</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 커널·펌웨어 하위 계층</t>
+          <t>파일리스·인메모리</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>OT-IR-01</t>
-        </is>
-      </c>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[CO] 수집</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-01.1</t>
+          <t>ENT-CO-01</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>프로세스 인젝션(인메모리 코드 주입)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>로컬·네트워크 공유 데이터 수집</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 시그니처 회피</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -2007,32 +2007,32 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[CO] 수집</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-04</t>
+          <t>ENT-CO-02</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>권한 상승 취약점 악용(로컬·커널)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>수집 데이터 압축·암호화 스테이징</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 시그니처 회피</t>
+          <t>암호화·정상 채널 은닉 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -2048,17 +2048,17 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-04</t>
+          <t>ENT-DE-04</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>도메인 프런팅·다단계 프록시</t>
+          <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -2068,17 +2068,17 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -2089,17 +2089,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>ENT-C2-06</t>
+          <t>ENT-DE-05</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>DNS 경유 C2·터널링</t>
+          <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>시그니처 회피 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -2130,17 +2130,17 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>ENT-CA-01.2</t>
+          <t>ENT-DE-06</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>캐시된 도메인 자격증명 추출</t>
+          <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리</t>
+          <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -2171,17 +2171,17 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>ENT-CA-04</t>
+          <t>ENT-DE-07</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>입력 캡처·키로깅</t>
+          <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리</t>
+          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
@@ -2212,17 +2212,17 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>[CO] 수집</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>ENT-CO-01</t>
+          <t>ENT-DE-08</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>로컬·네트워크 공유 데이터 수집</t>
+          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr"/>
@@ -2253,17 +2253,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>[CO] 수집</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>ENT-CO-02</t>
+          <t>ENT-EX-01.2</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>수집 데이터 압축·암호화 스테이징</t>
+          <t>Windows 관리 도구(WMI) 악용</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 시그니처 회피</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
@@ -2294,17 +2294,17 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-04</t>
+          <t>ENT-EX-03</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>위장(정상 이름·경로·서명 가장)</t>
+          <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
@@ -2335,17 +2335,17 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-05</t>
+          <t>ENT-EX-04</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>파일·정보 난독화·암호화</t>
+          <t>네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피 · 파일리스·인메모리</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -2376,17 +2376,17 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>ENT-DI-01</t>
+          <t>ENT-IA-03</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>호스트·시스템·네트워크 구성 탐색</t>
+          <t>드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>시그니처 회피 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -2417,17 +2417,17 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-01.2</t>
+          <t>ENT-IA-04</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Windows 관리 도구(WMI) 악용</t>
+          <t>이동식 매체·임시 접속 자산 경유 복제</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -2437,38 +2437,42 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>경계 밖·비관리 장비</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>OT-IA-05</t>
+        </is>
+      </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-04</t>
+          <t>ENT-IM-04</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>네이티브 API·시스템 서비스 실행</t>
+          <t>서비스 중지·시스템 종료/재시작</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -2478,12 +2482,12 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -2499,17 +2503,17 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-03</t>
+          <t>ENT-LM-03</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>드라이브바이 컴프로마이즈·워터링홀</t>
+          <t>측면 도구 전송</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -2519,12 +2523,12 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피 · 신뢰·공급 관계 경유</t>
+          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -2540,17 +2544,17 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-04</t>
+          <t>ENT-PE-01</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>이동식 매체·임시 접속 자산 경유 복제</t>
+          <t>윈도우 서비스 생성·수정</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -2560,12 +2564,12 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>경계 밖·비관리 장비</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -2573,29 +2577,25 @@
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>OT-IA-05</t>
-        </is>
-      </c>
+      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-04</t>
+          <t>ENT-PE-03</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>서비스 중지·시스템 종료/재시작</t>
+          <t>예약 작업(스케줄드 태스크)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -2626,17 +2626,17 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-03</t>
+          <t>ENT-PV-01.1</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>측면 도구 전송</t>
+          <t>프로세스 인젝션(인메모리 코드 주입)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
+          <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -2667,17 +2667,17 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-01</t>
+          <t>ENT-PV-03</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>윈도우 서비스 생성·수정</t>
+          <t>사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -2708,17 +2708,17 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-02</t>
+          <t>ENT-PV-04</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>부팅·로그온 자동 실행(레지스트리·시작 폴더)</t>
+          <t>권한 상승 취약점 악용(로컬·커널)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>커널·펌웨어 하위 계층 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -2749,32 +2749,32 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[CA] 자격증명 접근</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-03</t>
+          <t>ENT-CA-01.2</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>예약 작업(스케줄드 태스크)</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>캐시된 도메인 자격증명 추출</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 파일리스·인메모리</t>
+          <t>파일리스·인메모리</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -2790,77 +2790,73 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-04</t>
+          <t>ENT-DI-03</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>계정 조작·숨은 로컬 계정</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>보안 소프트웨어·방어 환경 탐색</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>ID-PE-02</t>
-        </is>
-      </c>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-01.2</t>
+          <t>ENT-PE-02</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>접근 토큰 조작</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>부팅·로그온 자동 실행(레지스트리·시작 폴더)</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 파일리스·인메모리</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -2876,58 +2872,62 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-03</t>
+          <t>ENT-PE-04</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>사용자 계정 컨트롤(UAC) 우회</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>계정 조작·숨은 로컬 계정</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>ID-PE-02</t>
+        </is>
+      </c>
       <c r="I53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>ENT-DI-03</t>
+          <t>ENT-PV-01.2</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>보안 소프트웨어·방어 환경 탐색</t>
+          <t>접근 토큰 조작</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>정상 인증 위장 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -3034,9 +3034,9 @@
           <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3071,9 +3071,9 @@
           <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3108,9 +3108,9 @@
           <t>Kerberoasting·AS-REP 로스팅</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3182,9 +3182,9 @@
           <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3219,9 +3219,9 @@
           <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3256,9 +3256,9 @@
           <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3552,9 +3552,9 @@
           <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3626,9 +3626,9 @@
           <t>계정 조작·숨은 로컬 계정</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">

--- a/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
+++ b/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">

--- a/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
+++ b/integrated/output/통합_보안위협_매트릭스_v5_엔터프라이즈뷰.xlsx
@@ -1204,17 +1204,17 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-DI-01</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
+          <t>호스트·시스템·네트워크 구성 탐색</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -1245,17 +1245,17 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-DI-02</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드(커널)</t>
+          <t>도메인·AD 열거(계정·신뢰·공유)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1286,17 +1286,17 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-DM-01.1</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
+          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피</t>
+          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ENT-DI-01</t>
+          <t>ENT-DM-01.2</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>호스트·시스템·네트워크 구성 탐색</t>
+          <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -1368,17 +1368,17 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[EF] 반출</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ENT-DI-02</t>
+          <t>ENT-EF-01</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>도메인·AD 열거(계정·신뢰·공유)</t>
+          <t>C2 채널 경유 반출</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1409,17 +1409,17 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>[EF] 반출</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ENT-EF-01</t>
+          <t>ENT-EX-01.1</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>C2 채널 경유 반출</t>
+          <t>PowerShell 악용(파일리스 실행)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1450,17 +1450,17 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PowerShell 악용(파일리스 실행)</t>
+          <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>경계 밖·비관리 장비 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1483,9 +1483,13 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>CL-IA-01</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
+          <t>ENT-IA-02</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
+          <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1511,12 +1515,12 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>경계 밖·비관리 장비 · 신뢰·공급 관계 경유</t>
+          <t>정상 인증 위장 · 경계 밖·비관리 장비</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -1526,27 +1530,27 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>CL-IA-01</t>
+          <t>CL-IA-02, ID-AU-04</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-02</t>
+          <t>ENT-IM-03</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
+          <t>데이터 파괴·와이퍼</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1556,12 +1560,12 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 경계 밖·비관리 장비</t>
+          <t>서명된 정상 도구 악용 · 커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1571,27 +1575,27 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>CL-IA-02, ID-AU-04</t>
+          <t>OT-IR-01</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-03</t>
+          <t>ENT-LM-01</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>데이터 파괴·와이퍼</t>
+          <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1601,12 +1605,12 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 커널·펌웨어 하위 계층</t>
+          <t>정상 인증 위장 · 암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1614,13 +1618,9 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>OT-IR-01</t>
-        </is>
-      </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-01</t>
+          <t>ENT-LM-02</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
+          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 암호화·정상 채널 은닉</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -1659,25 +1659,29 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>ID-TS-02</t>
+        </is>
+      </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-02</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
+          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1687,12 +1691,12 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>시그니처 회피</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -1700,13 +1704,9 @@
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>ID-TS-02</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2048,17 +2048,17 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-04</t>
+          <t>ENT-EX-01.2</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>위장(정상 이름·경로·서명 가장)</t>
+          <t>Windows 관리 도구(WMI) 악용</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -2068,17 +2068,17 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -2089,17 +2089,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-05</t>
+          <t>ENT-EX-03</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>파일·정보 난독화·암호화</t>
+          <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피 · 파일리스·인메모리</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -2130,17 +2130,17 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-EX-04</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>인메모리·반사 코드 로딩</t>
+          <t>네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 시그니처 회피</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -2171,17 +2171,17 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-07</t>
+          <t>ENT-IA-03</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>루트킷(사용자·커널 은폐)</t>
+          <t>드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
+          <t>시그니처 회피 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
@@ -2212,17 +2212,17 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-IA-04</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
+          <t>이동식 매체·임시 접속 자산 경유 복제</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2232,38 +2232,42 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>경계 밖·비관리 장비</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>OT-IA-05</t>
+        </is>
+      </c>
       <c r="I37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[IM] 영향</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-01.2</t>
+          <t>ENT-IM-04</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Windows 관리 도구(WMI) 악용</t>
+          <t>서비스 중지·시스템 종료/재시작</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2273,17 +2277,17 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
@@ -2294,17 +2298,17 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-03</t>
+          <t>ENT-LM-03</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
+          <t>측면 도구 전송</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2314,17 +2318,17 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
@@ -2335,17 +2339,17 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>ENT-EX-04</t>
+          <t>ENT-PE-01</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>네이티브 API·시스템 서비스 실행</t>
+          <t>윈도우 서비스 생성·수정</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -2355,12 +2359,12 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -2376,17 +2380,17 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[PE] 지속</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-03</t>
+          <t>ENT-PE-03</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>드라이브바이 컴프로마이즈·워터링홀</t>
+          <t>예약 작업(스케줄드 태스크)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2396,12 +2400,12 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>시그니처 회피 · 신뢰·공급 관계 경유</t>
+          <t>서명된 정상 도구 악용 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -2417,17 +2421,17 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ENT-IA-04</t>
+          <t>ENT-PV-01.1</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>이동식 매체·임시 접속 자산 경유 복제</t>
+          <t>프로세스 인젝션(인메모리 코드 주입)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -2437,12 +2441,12 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>경계 밖·비관리 장비</t>
+          <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -2450,29 +2454,25 @@
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>OT-IA-05</t>
-        </is>
-      </c>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>[IM] 영향</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>ENT-IM-04</t>
+          <t>ENT-PV-03</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>서비스 중지·시스템 종료/재시작</t>
+          <t>사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -2503,17 +2503,17 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[PV] 권한 상승</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>ENT-LM-03</t>
+          <t>ENT-PV-04</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>측면 도구 전송</t>
+          <t>권한 상승 취약점 악용(로컬·커널)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
+          <t>커널·펌웨어 하위 계층 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -2544,17 +2544,17 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-01</t>
+          <t>ENT-ST-02</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>윈도우 서비스 생성·수정</t>
+          <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -2585,17 +2585,17 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>[PE] 지속</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>ENT-PE-03</t>
+          <t>ENT-ST-03</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>예약 작업(스케줄드 태스크)</t>
+          <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 파일리스·인메모리</t>
+          <t>시그니처 회피 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -2626,17 +2626,17 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-01.1</t>
+          <t>ENT-ST-04</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>프로세스 인젝션(인메모리 코드 주입)</t>
+          <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
@@ -2667,17 +2667,17 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-03</t>
+          <t>ENT-ST-05</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>사용자 계정 컨트롤(UAC) 우회</t>
+          <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
@@ -2708,17 +2708,17 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>[PV] 권한 상승</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ENT-PV-04</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>권한 상승 취약점 악용(로컬·커널)</t>
+          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 시그니처 회피</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
